--- a/data/trans_dic/Q23_tabaco_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,27; 30,03</t>
+          <t>17,88; 29,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 29,28</t>
+          <t>17,15; 28,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,56; 31,08</t>
+          <t>17,55; 30,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,8; 31,1</t>
+          <t>17,96; 30,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 23,21</t>
+          <t>9,7; 23,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 26,73</t>
+          <t>13,28; 27,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,12; 30,79</t>
+          <t>15,57; 31,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,43; 26,06</t>
+          <t>14,54; 26,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,75; 25,45</t>
+          <t>16,64; 25,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,01; 26,19</t>
+          <t>17,34; 26,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,71; 28,7</t>
+          <t>18,57; 28,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 27,07</t>
+          <t>18,46; 27,33</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,82; 36,14</t>
+          <t>22,08; 35,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,72; 33,54</t>
+          <t>20,86; 33,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,63; 42,35</t>
+          <t>26,9; 41,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,89; 37,4</t>
+          <t>23,11; 38,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 32,63</t>
+          <t>19,37; 32,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 34,24</t>
+          <t>19,61; 34,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 27,33</t>
+          <t>15,07; 28,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,72; 33,97</t>
+          <t>20,07; 33,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,48; 31,99</t>
+          <t>21,59; 32,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,5; 31,2</t>
+          <t>21,7; 31,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,87; 33,24</t>
+          <t>23,59; 33,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,32; 33,63</t>
+          <t>23,69; 33,51</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,55; 39,74</t>
+          <t>28,98; 39,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,7; 43,17</t>
+          <t>33,11; 43,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,5; 44,59</t>
+          <t>33,43; 44,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 40,16</t>
+          <t>5,64; 40,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,02; 31,18</t>
+          <t>11,23; 31,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,44; 27,27</t>
+          <t>12,69; 27,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,15; 38,06</t>
+          <t>14,62; 37,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 35,72</t>
+          <t>15,2; 36,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,02; 36,4</t>
+          <t>26,83; 36,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,0; 38,35</t>
+          <t>30,06; 38,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,74; 41,97</t>
+          <t>31,71; 41,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 37,63</t>
+          <t>6,56; 37,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,38; 41,63</t>
+          <t>34,19; 41,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,73; 44,1</t>
+          <t>36,08; 43,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,62; 41,01</t>
+          <t>33,48; 40,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,22; 40,43</t>
+          <t>31,46; 40,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,4; 32,86</t>
+          <t>22,1; 32,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,13</t>
+          <t>23,87; 33,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,32; 29,13</t>
+          <t>19,73; 29,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,2; 31,6</t>
+          <t>21,23; 31,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,94; 37,94</t>
+          <t>32,12; 38,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,16; 39,06</t>
+          <t>33,4; 39,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,5; 35,36</t>
+          <t>29,34; 35,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,93; 35,45</t>
+          <t>29,0; 35,93</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,8; 50,63</t>
+          <t>35,72; 50,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,74; 43,87</t>
+          <t>33,06; 44,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,76; 44,5</t>
+          <t>33,73; 44,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,04; 47,33</t>
+          <t>34,07; 46,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,94; 38,02</t>
+          <t>24,94; 37,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,77; 36,02</t>
+          <t>24,67; 36,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,8; 39,19</t>
+          <t>28,33; 39,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,98; 29,53</t>
+          <t>19,64; 29,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,0; 42,65</t>
+          <t>32,9; 43,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,51; 38,49</t>
+          <t>30,23; 38,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,04; 40,5</t>
+          <t>33,04; 40,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,43; 36,89</t>
+          <t>28,69; 37,27</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35,28; 57,97</t>
+          <t>34,92; 58,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,78; 58,61</t>
+          <t>31,31; 57,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,84; 51,27</t>
+          <t>28,7; 51,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,31; 63,97</t>
+          <t>10,63; 61,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,87; 34,93</t>
+          <t>22,15; 34,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,43; 40,84</t>
+          <t>27,45; 40,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,72; 31,35</t>
+          <t>17,94; 30,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,76; 25,65</t>
+          <t>12,02; 25,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,66; 38,87</t>
+          <t>26,67; 38,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,04; 42,58</t>
+          <t>30,75; 42,53</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,21; 33,82</t>
+          <t>22,96; 32,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,74; 28,96</t>
+          <t>14,02; 30,84</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,03; 37,6</t>
+          <t>33,02; 37,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33,68; 38,11</t>
+          <t>33,74; 38,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,87; 38,54</t>
+          <t>34,15; 38,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,09; 35,08</t>
+          <t>17,3; 35,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,53; 29,1</t>
+          <t>23,43; 29,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,21; 30,46</t>
+          <t>25,1; 30,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,59; 28,58</t>
+          <t>23,56; 28,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,21; 26,15</t>
+          <t>21,22; 26,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,08; 33,78</t>
+          <t>30,16; 33,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,96; 34,3</t>
+          <t>30,94; 34,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,92; 33,62</t>
+          <t>30,25; 33,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,62; 30,55</t>
+          <t>19,92; 30,6</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40154; 65987</t>
+          <t>39294; 64503</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42695; 72588</t>
+          <t>42508; 70871</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34689; 61406</t>
+          <t>34674; 59525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38620; 63876</t>
+          <t>36897; 63585</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10467; 25990</t>
+          <t>10863; 26816</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18637; 38731</t>
+          <t>19232; 39637</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19561; 39839</t>
+          <t>20142; 40436</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19177; 34634</t>
+          <t>19327; 34909</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55574; 84405</t>
+          <t>55207; 85252</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66826; 102885</t>
+          <t>68128; 102888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61157; 93831</t>
+          <t>60723; 92001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62419; 91582</t>
+          <t>62449; 92453</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40504; 67087</t>
+          <t>40997; 66246</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47994; 77694</t>
+          <t>48333; 77179</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48573; 74439</t>
+          <t>47289; 73478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42011; 68653</t>
+          <t>42420; 70582</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29733; 51744</t>
+          <t>30718; 51020</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33208; 59089</t>
+          <t>33849; 58675</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22764; 43463</t>
+          <t>23963; 45367</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27387; 47177</t>
+          <t>27880; 46499</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77366; 110125</t>
+          <t>74304; 110149</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86931; 126108</t>
+          <t>87716; 126786</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76557; 111282</t>
+          <t>78970; 111337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75179; 108446</t>
+          <t>76398; 108055</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>87285; 121503</t>
+          <t>88609; 120657</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>132768; 175311</t>
+          <t>134428; 176384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105599; 140553</t>
+          <t>105396; 139896</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25294; 184287</t>
+          <t>25878; 184417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6724; 19022</t>
+          <t>6851; 19378</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14090; 30898</t>
+          <t>14376; 31135</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11028; 24480</t>
+          <t>9406; 24258</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7254; 16635</t>
+          <t>7078; 17162</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99086; 133491</t>
+          <t>98383; 134494</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>155821; 199177</t>
+          <t>156096; 199614</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120455; 159287</t>
+          <t>120344; 157404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25074; 190193</t>
+          <t>33160; 190343</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>244915; 296519</t>
+          <t>243544; 295242</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>286006; 343430</t>
+          <t>280983; 339051</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>217734; 265590</t>
+          <t>216857; 265454</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163014; 211079</t>
+          <t>164273; 209928</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59971; 87972</t>
+          <t>59170; 87611</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>92561; 129173</t>
+          <t>93086; 132029</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>81679; 117059</t>
+          <t>79296; 117473</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63621; 90544</t>
+          <t>60829; 89355</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>313067; 371801</t>
+          <t>314832; 374472</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>387512; 456453</t>
+          <t>390356; 459668</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>309572; 371088</t>
+          <t>307941; 372671</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>233924; 286692</t>
+          <t>234490; 290565</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80260; 110440</t>
+          <t>77920; 110335</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>105677; 141607</t>
+          <t>106714; 142168</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119710; 157780</t>
+          <t>119578; 158932</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83635; 116276</t>
+          <t>83697; 115307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>49304; 75158</t>
+          <t>49308; 74178</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69127; 100524</t>
+          <t>68844; 101218</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78566; 110777</t>
+          <t>80074; 111042</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42764; 66538</t>
+          <t>44252; 67318</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>137217; 177357</t>
+          <t>136787; 179683</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183593; 231635</t>
+          <t>181931; 231946</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>210546; 258080</t>
+          <t>210531; 257653</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>133918; 173764</t>
+          <t>135158; 175534</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26492; 43533</t>
+          <t>26227; 43629</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17553; 32370</t>
+          <t>17290; 31649</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21665; 38512</t>
+          <t>21558; 38898</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4233; 22007</t>
+          <t>3656; 21302</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43815; 69988</t>
+          <t>44378; 69336</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59134; 88043</t>
+          <t>59189; 88363</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38540; 64552</t>
+          <t>36950; 62048</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14232; 31036</t>
+          <t>14542; 31338</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>76204; 107071</t>
+          <t>73459; 105471</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84058; 115304</t>
+          <t>83272; 115188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65238; 95045</t>
+          <t>64528; 92648</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21346; 45001</t>
+          <t>21789; 47920</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>566973; 645433</t>
+          <t>566907; 644854</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>687887; 778300</t>
+          <t>689156; 782796</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>598173; 680633</t>
+          <t>603112; 683872</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>298535; 578752</t>
+          <t>285447; 580059</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>234697; 290245</t>
+          <t>233673; 289839</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>331582; 400702</t>
+          <t>330097; 400422</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>293267; 355366</t>
+          <t>292913; 356536</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>201816; 248737</t>
+          <t>201894; 247724</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>816244; 916724</t>
+          <t>818648; 916174</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1039695; 1151734</t>
+          <t>1038852; 1150670</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>900368; 1011628</t>
+          <t>910237; 1017155</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>510272; 794571</t>
+          <t>518157; 795979</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q23_tabaco_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,88; 29,36</t>
+          <t>17,94; 30,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,15; 28,59</t>
+          <t>17,59; 28,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,55; 30,13</t>
+          <t>17,49; 30,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,96; 30,96</t>
+          <t>17,89; 29,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 23,95</t>
+          <t>10,11; 24,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,28; 27,36</t>
+          <t>13,24; 28,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,57; 31,25</t>
+          <t>15,52; 31,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,54; 26,26</t>
+          <t>15,26; 26,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 25,7</t>
+          <t>16,92; 25,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,34; 26,19</t>
+          <t>17,2; 26,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,57; 28,14</t>
+          <t>18,7; 28,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,46; 27,33</t>
+          <t>18,44; 26,77</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,08; 35,68</t>
+          <t>21,87; 35,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,86; 33,32</t>
+          <t>21,06; 34,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,9; 41,8</t>
+          <t>27,66; 41,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,11; 38,45</t>
+          <t>22,02; 35,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,37; 32,17</t>
+          <t>18,33; 33,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,61; 34,0</t>
+          <t>19,29; 33,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,07; 28,53</t>
+          <t>14,54; 27,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,07; 33,48</t>
+          <t>19,84; 32,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,59; 32,0</t>
+          <t>22,44; 32,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 31,36</t>
+          <t>22,11; 31,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,59; 33,25</t>
+          <t>22,5; 32,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,69; 33,51</t>
+          <t>22,93; 31,8</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,98; 39,47</t>
+          <t>29,12; 39,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,11; 43,44</t>
+          <t>33,54; 43,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,43; 44,38</t>
+          <t>33,5; 44,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 40,19</t>
+          <t>30,47; 43,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 31,76</t>
+          <t>10,84; 30,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 27,48</t>
+          <t>12,3; 28,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,62; 37,71</t>
+          <t>16,43; 37,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 36,85</t>
+          <t>15,77; 34,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,83; 36,67</t>
+          <t>26,73; 36,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,06; 38,44</t>
+          <t>30,11; 38,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,71; 41,47</t>
+          <t>31,86; 42,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 37,66</t>
+          <t>29,18; 40,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,19; 41,45</t>
+          <t>34,27; 41,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,08; 43,54</t>
+          <t>36,47; 43,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,48; 40,99</t>
+          <t>33,78; 41,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,46; 40,21</t>
+          <t>31,53; 39,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,1; 32,73</t>
+          <t>22,14; 33,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,87; 33,86</t>
+          <t>24,04; 33,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,73; 29,23</t>
+          <t>21,01; 29,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 31,18</t>
+          <t>20,6; 29,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,12; 38,21</t>
+          <t>31,85; 37,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,4; 39,33</t>
+          <t>33,66; 38,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,34; 35,51</t>
+          <t>29,45; 35,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,0; 35,93</t>
+          <t>28,97; 35,22</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,72; 50,58</t>
+          <t>37,3; 50,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,06; 44,04</t>
+          <t>32,39; 43,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,73; 44,83</t>
+          <t>33,84; 44,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,07; 46,93</t>
+          <t>33,32; 45,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,94; 37,52</t>
+          <t>25,2; 39,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,67; 36,27</t>
+          <t>24,76; 35,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,33; 39,29</t>
+          <t>27,79; 39,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,64; 29,87</t>
+          <t>19,29; 28,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,9; 43,21</t>
+          <t>33,14; 43,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,23; 38,54</t>
+          <t>30,59; 38,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,04; 40,43</t>
+          <t>32,98; 40,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,69; 37,27</t>
+          <t>28,05; 35,57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,92; 58,09</t>
+          <t>35,14; 58,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,31; 57,31</t>
+          <t>31,39; 57,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,7; 51,78</t>
+          <t>28,0; 51,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,63; 61,92</t>
+          <t>10,38; 58,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,15; 34,61</t>
+          <t>21,82; 34,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,45; 40,99</t>
+          <t>27,93; 40,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,94; 30,13</t>
+          <t>17,83; 30,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,02; 25,9</t>
+          <t>11,77; 24,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,67; 38,29</t>
+          <t>27,04; 38,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,75; 42,53</t>
+          <t>30,64; 42,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,96; 32,96</t>
+          <t>23,36; 34,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 30,84</t>
+          <t>14,04; 27,45</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,02; 37,56</t>
+          <t>32,99; 37,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33,74; 38,33</t>
+          <t>33,73; 38,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,15; 38,73</t>
+          <t>33,87; 38,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,3; 35,16</t>
+          <t>31,11; 36,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,43; 29,06</t>
+          <t>23,33; 29,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,1; 30,44</t>
+          <t>25,23; 30,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,56; 28,68</t>
+          <t>23,56; 28,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,22; 26,04</t>
+          <t>20,91; 25,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,16; 33,76</t>
+          <t>30,27; 33,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,94; 34,27</t>
+          <t>31,07; 34,25</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,25; 33,8</t>
+          <t>30,15; 33,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,92; 30,6</t>
+          <t>27,66; 31,24</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49731</t>
+          <t>51509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26440</t>
+          <t>28894</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76172</t>
+          <t>80403</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39294; 64503</t>
+          <t>39409; 67093</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42508; 70871</t>
+          <t>43619; 70937</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34674; 59525</t>
+          <t>34556; 60394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36897; 63585</t>
+          <t>39608; 65479</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10863; 26816</t>
+          <t>11320; 26876</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19232; 39637</t>
+          <t>19186; 41616</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20142; 40436</t>
+          <t>20084; 40501</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19327; 34909</t>
+          <t>21552; 37545</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55207; 85252</t>
+          <t>56116; 85549</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68128; 102888</t>
+          <t>67575; 103798</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60723; 92001</t>
+          <t>61154; 92734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62449; 92453</t>
+          <t>66858; 97067</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54331</t>
+          <t>56010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36601</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90932</t>
+          <t>94687</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40997; 66246</t>
+          <t>40607; 65723</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48333; 77179</t>
+          <t>48779; 79095</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47289; 73478</t>
+          <t>48621; 73072</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42420; 70582</t>
+          <t>42861; 68718</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30718; 51020</t>
+          <t>29070; 52443</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33849; 58675</t>
+          <t>33295; 58348</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23963; 45367</t>
+          <t>23116; 43575</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27880; 46499</t>
+          <t>30454; 49595</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74304; 110149</t>
+          <t>77260; 110238</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87716; 126786</t>
+          <t>89390; 126881</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78970; 111337</t>
+          <t>75336; 109568</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76398; 108055</t>
+          <t>79826; 110707</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81916</t>
+          <t>85055</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93144</t>
+          <t>96740</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88609; 120657</t>
+          <t>89033; 121943</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>134428; 176384</t>
+          <t>136177; 175718</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105396; 139896</t>
+          <t>105604; 140293</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25878; 184417</t>
+          <t>70654; 100725</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6851; 19378</t>
+          <t>6612; 18373</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14376; 31135</t>
+          <t>13932; 31952</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9406; 24258</t>
+          <t>10570; 24267</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7078; 17162</t>
+          <t>7773; 17201</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98383; 134494</t>
+          <t>98038; 133954</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>156096; 199614</t>
+          <t>156374; 198238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120344; 157404</t>
+          <t>120916; 160327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33160; 190343</t>
+          <t>82042; 113133</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186233</t>
+          <t>203214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>75164</t>
+          <t>77463</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>261398</t>
+          <t>280677</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>243544; 295242</t>
+          <t>244093; 295179</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>280983; 339051</t>
+          <t>283965; 339703</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>216857; 265454</t>
+          <t>218791; 267698</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>164273; 209928</t>
+          <t>179230; 227193</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59170; 87611</t>
+          <t>59265; 89252</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93086; 132029</t>
+          <t>93735; 132228</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79296; 117473</t>
+          <t>84439; 118839</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60829; 89355</t>
+          <t>63848; 92113</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>314832; 374472</t>
+          <t>312102; 372344</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>390356; 459668</t>
+          <t>393348; 455535</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>307941; 372671</t>
+          <t>309078; 370822</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>234490; 290565</t>
+          <t>254483; 309356</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99417</t>
+          <t>107884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54497</t>
+          <t>59289</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>153914</t>
+          <t>167173</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77920; 110335</t>
+          <t>81352; 110957</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>106714; 142168</t>
+          <t>104559; 139831</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119578; 158932</t>
+          <t>119983; 158290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83697; 115307</t>
+          <t>92235; 126504</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>49308; 74178</t>
+          <t>49825; 77404</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68844; 101218</t>
+          <t>69079; 99991</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80074; 111042</t>
+          <t>78560; 110815</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>44252; 67318</t>
+          <t>48229; 72189</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>136787; 179683</t>
+          <t>137814; 179064</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>181931; 231946</t>
+          <t>184116; 230768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>210531; 257653</t>
+          <t>210179; 260511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>135158; 175534</t>
+          <t>147800; 187415</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>22267</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31815</t>
+          <t>31119</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26227; 43629</t>
+          <t>26390; 44010</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17290; 31649</t>
+          <t>17337; 31817</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21558; 38898</t>
+          <t>21036; 38330</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3656; 21302</t>
+          <t>3300; 18581</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44378; 69336</t>
+          <t>43710; 68234</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59189; 88363</t>
+          <t>60206; 87572</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36950; 62048</t>
+          <t>36718; 62028</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14542; 31338</t>
+          <t>14971; 31581</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>73459; 105471</t>
+          <t>74492; 105342</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>83272; 115188</t>
+          <t>82981; 115852</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64528; 92648</t>
+          <t>65663; 96137</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21789; 47920</t>
+          <t>22319; 43651</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>481671</t>
+          <t>512524</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>225703</t>
+          <t>238275</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>707375</t>
+          <t>750798</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>566907; 644854</t>
+          <t>566303; 647342</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>689156; 782796</t>
+          <t>688887; 776648</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>603112; 683872</t>
+          <t>598029; 678638</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285447; 580059</t>
+          <t>474448; 551915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>233673; 289839</t>
+          <t>232670; 290600</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>330097; 400422</t>
+          <t>331814; 403981</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>292913; 356536</t>
+          <t>292915; 354513</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>201894; 247724</t>
+          <t>215601; 262541</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>818648; 916174</t>
+          <t>821443; 915733</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1038852; 1150670</t>
+          <t>1043181; 1149846</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>910237; 1017155</t>
+          <t>907365; 1009526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>518157; 795979</t>
+          <t>707086; 798506</t>
         </is>
       </c>
     </row>
